--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97679</v>
+        <v>97681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97681</v>
+        <v>97687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79732</v>
+        <v>79736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79732</v>
+        <v>79736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97687</v>
+        <v>97689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79736</v>
+        <v>79738</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79736</v>
+        <v>79738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97689</v>
+        <v>97690</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97690</v>
+        <v>97696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97696</v>
+        <v>97700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97700</v>
+        <v>97702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97704</v>
+        <v>97717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136769418</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>136769421</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>136769425</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136769426</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136769433</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>136769441</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>136769442</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>136769444</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97717</v>
+        <v>97719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136769418</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>136769421</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>136769425</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136769426</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136769433</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>136769441</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>136769442</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>136769444</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -2837,11 +2837,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -2959,11 +2955,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -3081,11 +3073,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -3203,11 +3191,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -3325,11 +3309,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -3447,11 +3427,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -3690,11 +3666,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97719</v>
+        <v>97722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97722</v>
+        <v>97732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136769418</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>136769421</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136769425</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136769426</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>136769433</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136769441</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136769442</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136769444</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97732</v>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97733</v>
+        <v>97738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769423</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769432</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136769427</v>
       </c>
       <c r="B9" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136769437</v>
       </c>
       <c r="B10" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136769429</v>
       </c>
       <c r="B11" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136769430</v>
       </c>
       <c r="B12" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136769434</v>
       </c>
       <c r="B13" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136769439</v>
       </c>
       <c r="B14" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136769440</v>
       </c>
       <c r="B15" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136769446</v>
       </c>
       <c r="B16" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136769428</v>
       </c>
       <c r="B17" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136769436</v>
       </c>
       <c r="B18" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136769431</v>
       </c>
       <c r="B19" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136769435</v>
       </c>
       <c r="B20" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136769418</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>136769421</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136769425</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136769426</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>136769433</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136769441</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136769442</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136769444</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60817-2024 artfynd.xlsx
+++ b/artfynd/A 60817-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769420</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769447</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769422</v>
       </c>
       <c r="B4" t="n">
-        <v>97738</v>
+        <v>97740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769448</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769438</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>136769424</v>
       </c>
       <c r="B29" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>136769445</v>
       </c>
       <c r="B30" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
